--- a/Sindhi Muslim/Result Sheet/Final Term March-2025/Result Summary.xlsx
+++ b/Sindhi Muslim/Result Sheet/Final Term March-2025/Result Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\Final Term March-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1C646E-75AC-4151-8F2D-503EB06AE820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C865BB0-3EE6-48A9-BBF6-3676BF86CBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{234222B7-5806-4275-9FF5-29914A8FDB7D}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
   <si>
     <t>Grades</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Nine</t>
   </si>
   <si>
-    <t>Ten</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -164,6 +161,9 @@
   </si>
   <si>
     <t>Level-III</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -173,7 +173,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,23 +190,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -236,7 +256,37 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -246,11 +296,157 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -259,22 +455,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -590,265 +827,529 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{962DDA3B-2BA5-4642-AA1E-6F82F2EF2941}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="12"/>
+      <c r="H1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9" t="s">
+      <c r="I1" s="12"/>
+      <c r="J1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="9"/>
-      <c r="L1" s="7" t="s">
+      <c r="K1" s="12"/>
+      <c r="L1" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="16"/>
+    </row>
+    <row r="3" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="6">
+        <v>61</v>
+      </c>
+      <c r="C3" s="6">
+        <v>49</v>
+      </c>
+      <c r="D3" s="6">
+        <v>61</v>
+      </c>
+      <c r="E3" s="7">
+        <v>48</v>
+      </c>
+      <c r="F3" s="7">
+        <f>B3-D3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <f>C3-E3</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="7">
+        <f>D3-J3</f>
+        <v>51</v>
+      </c>
+      <c r="I3" s="7">
+        <f>E3-K3</f>
+        <v>43</v>
+      </c>
+      <c r="J3" s="6">
+        <v>10</v>
+      </c>
+      <c r="K3" s="6">
+        <v>5</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="7">
+        <v>32</v>
+      </c>
+      <c r="C4" s="7">
+        <v>24</v>
+      </c>
+      <c r="D4" s="7">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7">
+        <v>23</v>
+      </c>
+      <c r="F4" s="7">
+        <f>B4-D4</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="7">
+        <f>C4-E4</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="7">
+        <f>D4-J4</f>
+        <v>31</v>
+      </c>
+      <c r="I4" s="7">
+        <f>E4-K4</f>
+        <v>23</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7">
+        <v>23</v>
+      </c>
+      <c r="D5" s="7">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7">
+        <v>23</v>
+      </c>
+      <c r="F5" s="7">
+        <f>B5-D5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <f>C5-E5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <f>D5-J5</f>
+        <v>24</v>
+      </c>
+      <c r="I5" s="7">
+        <f>E5-K5</f>
+        <v>23</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7">
+        <v>26</v>
+      </c>
+      <c r="E6" s="7">
+        <v>24</v>
+      </c>
+      <c r="F6" s="7">
+        <f>B6-D6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <f>C6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <f>D6-J6</f>
+        <v>24</v>
+      </c>
+      <c r="I6" s="7">
+        <f>E6-K6</f>
+        <v>24</v>
+      </c>
+      <c r="J6" s="7">
+        <v>2</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="7">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7">
+        <v>30</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7">
+        <v>30</v>
+      </c>
+      <c r="F7" s="7">
+        <f>B7-D7</f>
+        <v>2</v>
+      </c>
+      <c r="G7" s="7">
+        <f>C7-E7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <f>D7-J7</f>
+        <v>16</v>
+      </c>
+      <c r="I7" s="7">
+        <f>E7-K7</f>
+        <v>25</v>
+      </c>
+      <c r="J7" s="7">
+        <v>4</v>
+      </c>
+      <c r="K7" s="7">
+        <v>5</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="7">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7">
+        <v>23</v>
+      </c>
+      <c r="D8" s="7">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7">
+        <f>B8-D8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <f>C8-E8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <f>D8-J8</f>
+        <v>21</v>
+      </c>
+      <c r="I8" s="7">
+        <f>E8-K8</f>
+        <v>22</v>
+      </c>
+      <c r="J8" s="7">
+        <v>2</v>
+      </c>
+      <c r="K8" s="7">
+        <v>1</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7">
+        <v>25</v>
+      </c>
+      <c r="D9" s="7">
+        <v>16</v>
+      </c>
+      <c r="E9" s="7">
+        <v>25</v>
+      </c>
+      <c r="F9" s="7">
+        <f>B9-D9</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <f>C9-E9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <f>D9-J9</f>
+        <v>12</v>
+      </c>
+      <c r="I9" s="7">
+        <f>E9-K9</f>
+        <v>21</v>
+      </c>
+      <c r="J9" s="7">
+        <v>4</v>
+      </c>
+      <c r="K9" s="7">
+        <v>4</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="7">
+        <v>27</v>
+      </c>
+      <c r="C10" s="7">
+        <v>18</v>
+      </c>
+      <c r="D10" s="7">
+        <v>26</v>
+      </c>
+      <c r="E10" s="7">
+        <v>17</v>
+      </c>
+      <c r="F10" s="7">
+        <f>B10-D10</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="7">
+        <f>C10-E10</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="7">
+        <f>D10-J10</f>
+        <v>19</v>
+      </c>
+      <c r="I10" s="7">
+        <f>E10-K10</f>
+        <v>16</v>
+      </c>
+      <c r="J10" s="7">
+        <v>7</v>
+      </c>
+      <c r="K10" s="7">
+        <v>1</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="7">
+        <v>19</v>
+      </c>
+      <c r="C11" s="7">
+        <v>23</v>
+      </c>
+      <c r="D11" s="7">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7">
+        <v>20</v>
+      </c>
+      <c r="F11" s="7">
+        <f>B11-D11</f>
         <v>3</v>
       </c>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="G11" s="7">
+        <f>C11-E11</f>
+        <v>3</v>
+      </c>
+      <c r="H11" s="7">
+        <f>D11-J11</f>
         <v>14</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="I11" s="7">
+        <f>E11-K11</f>
+        <v>19</v>
+      </c>
+      <c r="J11" s="7">
+        <v>2</v>
+      </c>
+      <c r="K11" s="7">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="9">
         <v>16</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="C12" s="9">
+        <v>19</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="7">
+        <f>B12-D12</f>
+        <v>16</v>
+      </c>
+      <c r="G12" s="7">
+        <f>C12-E12</f>
+        <v>19</v>
+      </c>
+      <c r="H12" s="7">
+        <f>D12-J12</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="7">
+        <f>E12-K12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="18">
+        <f>SUM(B3:B12)</f>
+        <v>267</v>
+      </c>
+      <c r="C13" s="18">
+        <f t="shared" ref="C13:K13" si="0">SUM(C3:C12)</f>
+        <v>258</v>
+      </c>
+      <c r="D13" s="18">
+        <f t="shared" si="0"/>
+        <v>243</v>
+      </c>
+      <c r="E13" s="18">
+        <f t="shared" si="0"/>
+        <v>233</v>
+      </c>
+      <c r="F13" s="18">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G13" s="18">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H13" s="18">
+        <f t="shared" si="0"/>
+        <v>212</v>
+      </c>
+      <c r="I13" s="18">
+        <f t="shared" si="0"/>
+        <v>216</v>
+      </c>
+      <c r="J13" s="18">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="K13" s="18">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="L13" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -873,7 +1374,7 @@
     <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="19.140625" bestFit="1" customWidth="1"/>
@@ -882,34 +1383,34 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -920,25 +1421,25 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="5">
+        <v>45682</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="6">
-        <v>45682</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J3" s="1">
         <v>45</v>
@@ -949,28 +1450,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5">
+        <v>45689</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="6">
-        <v>45689</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J4" s="1">
         <v>23</v>
@@ -981,28 +1482,28 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="5">
+        <v>45689</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6">
-        <v>45689</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J5" s="1">
         <v>38</v>
@@ -1013,28 +1514,28 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="5">
+        <v>45689</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="6">
-        <v>45689</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1">
         <v>41</v>
@@ -1048,28 +1549,28 @@
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="5">
+        <v>45769</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E7" s="6">
-        <v>45769</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H7" s="1">
         <v>4</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1079,7 +1580,7 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="6"/>
+      <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>

--- a/Sindhi Muslim/Result Sheet/Final Term March-2025/Result Summary.xlsx
+++ b/Sindhi Muslim/Result Sheet/Final Term March-2025/Result Summary.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\Final Term March-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C865BB0-3EE6-48A9-BBF6-3676BF86CBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F707A597-3516-43E8-A214-0BD52FEE54CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{234222B7-5806-4275-9FF5-29914A8FDB7D}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{234222B7-5806-4275-9FF5-29914A8FDB7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>Grades</t>
   </si>
@@ -91,76 +90,7 @@
     <t>Eight</t>
   </si>
   <si>
-    <t>Nine</t>
-  </si>
-  <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>S No</t>
-  </si>
-  <si>
-    <t>Event Name</t>
-  </si>
-  <si>
-    <t>Event Date</t>
-  </si>
-  <si>
-    <t>Event Duration</t>
-  </si>
-  <si>
-    <t>Teacher Participants</t>
-  </si>
-  <si>
-    <t>Student Participants</t>
-  </si>
-  <si>
-    <t>Event Location</t>
-  </si>
-  <si>
-    <t>Earth Day</t>
-  </si>
-  <si>
-    <t>SJCHS</t>
-  </si>
-  <si>
-    <t>2 Hours</t>
-  </si>
-  <si>
-    <t>Event Time</t>
-  </si>
-  <si>
-    <t>10:00 AM to 12:00 PM</t>
-  </si>
-  <si>
-    <t>50+</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>PTM</t>
-  </si>
-  <si>
-    <t>09:00 AM to 12:00 PM</t>
-  </si>
-  <si>
-    <t>3 Hours</t>
-  </si>
-  <si>
-    <t>Parents Participants</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Level-I</t>
-  </si>
-  <si>
-    <t>Level-II</t>
-  </si>
-  <si>
-    <t>Level-III</t>
   </si>
   <si>
     <t>Pass</t>
@@ -170,19 +100,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -226,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -383,36 +302,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -455,62 +344,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -827,529 +702,497 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{962DDA3B-2BA5-4642-AA1E-6F82F2EF2941}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12" t="s">
+      <c r="G1" s="10"/>
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12" t="s">
+      <c r="I1" s="10"/>
+      <c r="J1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13" t="s">
+      <c r="K1" s="10"/>
+      <c r="L1" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="16"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="1">
         <v>61</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="1">
         <v>49</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="1">
         <v>61</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="2">
         <v>48</v>
       </c>
-      <c r="F3" s="7">
-        <f>B3-D3</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
-        <f>C3-E3</f>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F11" si="0">B3-D3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G11" si="1">C3-E3</f>
         <v>1</v>
       </c>
-      <c r="H3" s="7">
-        <f>D3-J3</f>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H11" si="2">D3-J3</f>
         <v>51</v>
       </c>
-      <c r="I3" s="7">
-        <f>E3-K3</f>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I11" si="3">E3-K3</f>
         <v>43</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="1">
         <v>10</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="1">
         <v>5</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>42</v>
+      <c r="L3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="2">
         <v>32</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="2">
         <v>24</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="2">
         <v>31</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="2">
         <v>23</v>
       </c>
-      <c r="F4" s="7">
-        <f>B4-D4</f>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G4" s="7">
-        <f>C4-E4</f>
+      <c r="G4" s="2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H4" s="7">
-        <f>D4-J4</f>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="I4" s="7">
-        <f>E4-K4</f>
+      <c r="I4" s="2">
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>42</v>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="2">
         <v>24</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="2">
         <v>23</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="2">
         <v>24</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="2">
         <v>23</v>
       </c>
-      <c r="F5" s="7">
-        <f>B5-D5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="7">
-        <f>C5-E5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <f>D5-J5</f>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="I5" s="7">
-        <f>E5-K5</f>
+      <c r="I5" s="2">
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>42</v>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="2">
         <v>26</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="2">
         <v>24</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="2">
         <v>26</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="2">
         <v>24</v>
       </c>
-      <c r="F6" s="7">
-        <f>B6-D6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <f>C6-E6</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
-        <f>D6-J6</f>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="I6" s="7">
-        <f>E6-K6</f>
+      <c r="I6" s="2">
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="2">
         <v>2</v>
       </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>42</v>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="2">
         <v>22</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="2">
         <v>30</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="2">
         <v>20</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="2">
         <v>30</v>
       </c>
-      <c r="F7" s="7">
-        <f>B7-D7</f>
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G7" s="7">
-        <f>C7-E7</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
-        <f>D7-J7</f>
+      <c r="G7" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="I7" s="7">
-        <f>E7-K7</f>
+      <c r="I7" s="2">
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="2">
         <v>4</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="2">
         <v>5</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>42</v>
+      <c r="L7" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="2">
         <v>23</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="2">
         <v>23</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="2">
         <v>23</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="2">
         <v>23</v>
       </c>
-      <c r="F8" s="7">
-        <f>B8-D8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="7">
-        <f>C8-E8</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
-        <f>D8-J8</f>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="I8" s="7">
-        <f>E8-K8</f>
+      <c r="I8" s="2">
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="2">
         <v>2</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>42</v>
+      <c r="L8" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="2">
         <v>17</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="2">
         <v>25</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="2">
         <v>16</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="2">
         <v>25</v>
       </c>
-      <c r="F9" s="7">
-        <f>B9-D9</f>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G9" s="7">
-        <f>C9-E9</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <f>D9-J9</f>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="I9" s="7">
-        <f>E9-K9</f>
+      <c r="I9" s="2">
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="2">
         <v>4</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="2">
         <v>4</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>42</v>
+      <c r="L9" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="2">
         <v>27</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="2">
         <v>18</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="2">
         <v>26</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="2">
         <v>17</v>
       </c>
-      <c r="F10" s="7">
-        <f>B10-D10</f>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G10" s="7">
-        <f>C10-E10</f>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H10" s="7">
-        <f>D10-J10</f>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="I10" s="7">
-        <f>E10-K10</f>
+      <c r="I10" s="2">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="2">
         <v>7</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="2">
         <v>1</v>
       </c>
-      <c r="L10" s="8" t="s">
-        <v>42</v>
+      <c r="L10" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="2">
         <v>19</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="2">
         <v>23</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="2">
         <v>16</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="2">
         <v>20</v>
       </c>
-      <c r="F11" s="7">
-        <f>B11-D11</f>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G11" s="7">
-        <f>C11-E11</f>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="H11" s="7">
-        <f>D11-J11</f>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="I11" s="7">
-        <f>E11-K11</f>
+      <c r="I11" s="2">
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="2">
         <v>2</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>42</v>
+      <c r="L11" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="9">
-        <v>16</v>
-      </c>
-      <c r="C12" s="9">
-        <v>19</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="7">
-        <f>B12-D12</f>
-        <v>16</v>
-      </c>
-      <c r="G12" s="7">
-        <f>C12-E12</f>
-        <v>19</v>
-      </c>
-      <c r="H12" s="7">
-        <f>D12-J12</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="7">
-        <f>E12-K12</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="18">
-        <f>SUM(B3:B12)</f>
-        <v>267</v>
-      </c>
-      <c r="C13" s="18">
-        <f t="shared" ref="C13:K13" si="0">SUM(C3:C12)</f>
-        <v>258</v>
-      </c>
-      <c r="D13" s="18">
-        <f t="shared" si="0"/>
+      <c r="B12" s="6">
+        <f>SUM(B3:B11)</f>
+        <v>251</v>
+      </c>
+      <c r="C12" s="6">
+        <f>SUM(C3:C11)</f>
+        <v>239</v>
+      </c>
+      <c r="D12" s="6">
+        <f>SUM(D3:D11)</f>
         <v>243</v>
       </c>
-      <c r="E13" s="18">
-        <f t="shared" si="0"/>
+      <c r="E12" s="6">
+        <f>SUM(E3:E11)</f>
         <v>233</v>
       </c>
-      <c r="F13" s="18">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="G13" s="18">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="H13" s="18">
-        <f t="shared" si="0"/>
+      <c r="F12" s="6">
+        <f>SUM(F3:F11)</f>
+        <v>8</v>
+      </c>
+      <c r="G12" s="6">
+        <f>SUM(G3:G11)</f>
+        <v>6</v>
+      </c>
+      <c r="H12" s="6">
+        <f>SUM(H3:H11)</f>
         <v>212</v>
       </c>
-      <c r="I13" s="18">
-        <f t="shared" si="0"/>
+      <c r="I12" s="6">
+        <f>SUM(I3:I11)</f>
         <v>216</v>
       </c>
-      <c r="J13" s="18">
-        <f t="shared" si="0"/>
+      <c r="J12" s="6">
+        <f>SUM(J3:J11)</f>
         <v>31</v>
       </c>
-      <c r="K13" s="18">
-        <f t="shared" si="0"/>
+      <c r="K12" s="6">
+        <f>SUM(K3:K11)</f>
         <v>17</v>
       </c>
-      <c r="L13" s="19"/>
+      <c r="L12" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1363,231 +1206,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F37BEE7A-5834-4D31-B1B5-D4BA68F1615C}">
-  <dimension ref="A2:J8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5">
-        <v>45682</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="5">
-        <v>45689</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="5">
-        <v>45689</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="1">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="5">
-        <v>45689</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="5">
-        <v>45769</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="1">
-        <v>4</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>